--- a/admin-ui/src/locale/i18n.xlsx
+++ b/admin-ui/src/locale/i18n.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="12375" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27945" windowHeight="12375" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="lang" sheetId="4" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="667">
   <si>
     <t>支持的语言列表（实际表格，按照顺序列填写文言）</t>
   </si>
@@ -1744,6 +1744,303 @@
   </si>
   <si>
     <t>请输入摘要</t>
+  </si>
+  <si>
+    <t>menu.BlogBanner</t>
+  </si>
+  <si>
+    <t>链接</t>
+  </si>
+  <si>
+    <t>banner.add</t>
+  </si>
+  <si>
+    <t>创建链接</t>
+  </si>
+  <si>
+    <t>banner.add.sub</t>
+  </si>
+  <si>
+    <t>创建一个新链接</t>
+  </si>
+  <si>
+    <t>banner.del.tips</t>
+  </si>
+  <si>
+    <t>是否确认删除此链接？删除后不可恢复，当前链接存在是无法删除。</t>
+  </si>
+  <si>
+    <t>banner.edit</t>
+  </si>
+  <si>
+    <t>编辑链接</t>
+  </si>
+  <si>
+    <t>banner.get</t>
+  </si>
+  <si>
+    <t>查看链接</t>
+  </si>
+  <si>
+    <t>banner.sourceId</t>
+  </si>
+  <si>
+    <t>链接主图</t>
+  </si>
+  <si>
+    <t>banner.summary</t>
+  </si>
+  <si>
+    <t>链接简介</t>
+  </si>
+  <si>
+    <t>banner.summary.place</t>
+  </si>
+  <si>
+    <t>请输入链接简介</t>
+  </si>
+  <si>
+    <t>banner.tag</t>
+  </si>
+  <si>
+    <t>链接标签</t>
+  </si>
+  <si>
+    <t>banner.tag.place</t>
+  </si>
+  <si>
+    <t>请输入链接标签，仅用于展示</t>
+  </si>
+  <si>
+    <t>banner.title</t>
+  </si>
+  <si>
+    <t>链接名称</t>
+  </si>
+  <si>
+    <t>banner.title.place</t>
+  </si>
+  <si>
+    <t>请输入链接名称，全局唯一</t>
+  </si>
+  <si>
+    <t>banner.title.sc</t>
+  </si>
+  <si>
+    <t>请输入链接名称，支持模糊</t>
+  </si>
+  <si>
+    <t>banner.url</t>
+  </si>
+  <si>
+    <t>链接地址</t>
+  </si>
+  <si>
+    <t>banner.url.place</t>
+  </si>
+  <si>
+    <t>请输入链接地址</t>
+  </si>
+  <si>
+    <t>banner.url.sc</t>
+  </si>
+  <si>
+    <t>请输入链接地址，支持模糊</t>
+  </si>
+  <si>
+    <t>banner.type</t>
+  </si>
+  <si>
+    <t>链接类型</t>
+  </si>
+  <si>
+    <t>page.add</t>
+  </si>
+  <si>
+    <t>创建页面</t>
+  </si>
+  <si>
+    <t>page.add.sub</t>
+  </si>
+  <si>
+    <t>创建一个新页面</t>
+  </si>
+  <si>
+    <t>page.del.tips</t>
+  </si>
+  <si>
+    <t>是否确认删除此页面？删除后不可恢复，删除页面会同步删除页面关联。</t>
+  </si>
+  <si>
+    <t>page.edit</t>
+  </si>
+  <si>
+    <t>编辑页面</t>
+  </si>
+  <si>
+    <t>page.get</t>
+  </si>
+  <si>
+    <t>查看页面</t>
+  </si>
+  <si>
+    <t>post.add</t>
+  </si>
+  <si>
+    <t>创建文章</t>
+  </si>
+  <si>
+    <t>post.add.sub</t>
+  </si>
+  <si>
+    <t>创建一个新文章</t>
+  </si>
+  <si>
+    <t>post.banner</t>
+  </si>
+  <si>
+    <t>post.del.tips</t>
+  </si>
+  <si>
+    <t>是否确认删除此文章？删除后不可恢复，删除文章会同步删除文章关联。</t>
+  </si>
+  <si>
+    <t>post.edit</t>
+  </si>
+  <si>
+    <t>编辑文章</t>
+  </si>
+  <si>
+    <t>post.get</t>
+  </si>
+  <si>
+    <t>查看文章</t>
+  </si>
+  <si>
+    <t>post.pushAt</t>
+  </si>
+  <si>
+    <t>发布</t>
+  </si>
+  <si>
+    <t>post.pushAt.place</t>
+  </si>
+  <si>
+    <t>选择日期用于指定日期自动发布</t>
+  </si>
+  <si>
+    <t>post.tags.tips</t>
+  </si>
+  <si>
+    <t>请选择关联标签，点击右侧+添加新标签</t>
+  </si>
+  <si>
+    <t>source.check</t>
+  </si>
+  <si>
+    <t>资源快捷选择</t>
+  </si>
+  <si>
+    <t>tags.Edit</t>
+  </si>
+  <si>
+    <t>标签快捷创建</t>
+  </si>
+  <si>
+    <t>menu.BlogLinks</t>
+  </si>
+  <si>
+    <t>友链</t>
+  </si>
+  <si>
+    <t>links.add</t>
+  </si>
+  <si>
+    <t>links.add.sub</t>
+  </si>
+  <si>
+    <t>links.del.tips</t>
+  </si>
+  <si>
+    <t>links.edit</t>
+  </si>
+  <si>
+    <t>links.get</t>
+  </si>
+  <si>
+    <t>links.sourceId</t>
+  </si>
+  <si>
+    <t>links.summary</t>
+  </si>
+  <si>
+    <t>links.summary.place</t>
+  </si>
+  <si>
+    <t>links.title</t>
+  </si>
+  <si>
+    <t>links.title.place</t>
+  </si>
+  <si>
+    <t>links.title.sc</t>
+  </si>
+  <si>
+    <t>links.url</t>
+  </si>
+  <si>
+    <t>links.url.place</t>
+  </si>
+  <si>
+    <t>links.url.sc</t>
+  </si>
+  <si>
+    <t>创建友链</t>
+  </si>
+  <si>
+    <t>创建一个文章新友链</t>
+  </si>
+  <si>
+    <t>是否确认删除此友链？删除后不可恢复，当前友链存在文章是无法删除。</t>
+  </si>
+  <si>
+    <t>编辑友链</t>
+  </si>
+  <si>
+    <t>查看友链</t>
+  </si>
+  <si>
+    <t>友链主图</t>
+  </si>
+  <si>
+    <t>友链简介</t>
+  </si>
+  <si>
+    <t>请输入友链简介</t>
+  </si>
+  <si>
+    <t>友链名称</t>
+  </si>
+  <si>
+    <t>请输入友链名称，全局唯一</t>
+  </si>
+  <si>
+    <t>请输入友链名称，支持模糊</t>
+  </si>
+  <si>
+    <t>友链地址</t>
+  </si>
+  <si>
+    <t>请输入友链地址，全局唯一</t>
+  </si>
+  <si>
+    <t>请输入友链地址，支持模糊</t>
+  </si>
+  <si>
+    <t>links.status</t>
+  </si>
+  <si>
+    <t>友链状态</t>
   </si>
 </sst>
 </file>
@@ -1813,7 +2110,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1830,9 +2127,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2125,7 +2419,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B75"/>
+  <dimension ref="A1:B123"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="24.875" bestFit="1" customWidth="1"/>
@@ -2141,595 +2435,979 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A3" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A4" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A5" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A6" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A7" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A8" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A9" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A10" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A11" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A12" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A13" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A14" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A15" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A16" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A17" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A18" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A19" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B19" s="1" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A3" s="2" t="s">
+    <row r="20" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A20" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A4" s="2" t="s">
+    <row r="21" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A21" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A5" s="2" t="s">
+    <row r="22" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A22" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A6" s="2" t="s">
+    <row r="23" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A23" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A7" s="2" t="s">
+    <row r="24" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A24" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A8" s="2" t="s">
+    <row r="25" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A25" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B25" s="1" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A9" s="2" t="s">
+    <row r="26" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A26" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B26" s="1" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A10" s="2" t="s">
+    <row r="27" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A27" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B27" s="1" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A11" s="2" t="s">
+    <row r="28" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A28" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A12" s="2" t="s">
+    <row r="29" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A29" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B29" s="1" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A13" s="2" t="s">
+    <row r="30" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A30" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B30" s="1" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A14" s="2" t="s">
+    <row r="31" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A31" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B31" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A15" s="2" t="s">
+    <row r="32" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A32" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B32" s="1" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A16" s="2" t="s">
+    <row r="33" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A33" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B33" s="1" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A17" s="2" t="s">
+    <row r="34" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A34" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B34" s="1" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A18" s="2" t="s">
+    <row r="35" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A35" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B35" s="1" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A19" s="4" t="s">
+    <row r="36" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A36" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A37" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A38" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A39" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A40" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A41" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A42" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A43" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A44" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B44" s="1" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A20" s="2" t="s">
+    <row r="45" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A45" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A46" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A47" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A48" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B48" s="1" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A21" s="2" t="s">
+    <row r="49" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A49" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B49" s="1" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A22" s="2" t="s">
+    <row r="50" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A50" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A51" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A52" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B52" s="1" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A23" s="2" t="s">
+    <row r="53" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A53" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B53" s="1" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A24" s="2" t="s">
+    <row r="54" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A54" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B54" s="1" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A25" s="2" t="s">
+    <row r="55" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A55" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B55" s="1" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A26" s="2" t="s">
+    <row r="56" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A56" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A57" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B57" s="1" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A27" s="2" t="s">
+    <row r="58" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A58" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B58" s="1" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A28" s="4" t="s">
+    <row r="59" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A59" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B59" s="1" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A29" s="2" t="s">
+    <row r="60" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A60" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B60" s="1" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A30" s="2" t="s">
+    <row r="61" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A61" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B61" s="1" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A31" s="2" t="s">
+    <row r="62" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A62" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B62" s="1" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A32" s="2" t="s">
+    <row r="63" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A63" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B63" s="1" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A33" s="2" t="s">
+    <row r="64" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A64" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B64" s="1" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A34" s="2" t="s">
+    <row r="65" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A65" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A66" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B66" s="1" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A35" s="2" t="s">
+    <row r="67" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A67" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B67" s="1" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A36" s="2" t="s">
+    <row r="68" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A68" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B68" s="1" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A37" s="2" t="s">
+    <row r="69" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A69" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B69" s="1" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A38" s="2" t="s">
+    <row r="70" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A70" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B70" s="1" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A39" s="2" t="s">
+    <row r="71" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A71" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B71" s="1" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A40" s="2" t="s">
+    <row r="72" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A72" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B72" s="1" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A41" s="2" t="s">
+    <row r="73" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A73" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B73" s="1" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A42" s="2" t="s">
+    <row r="74" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A74" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B74" s="1" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A43" s="2" t="s">
+    <row r="75" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A75" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B75" s="1" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A44" s="2" t="s">
+    <row r="76" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A76" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B76" s="1" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A45" s="2" t="s">
+    <row r="77" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A77" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B77" s="1" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A46" s="2" t="s">
+    <row r="78" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A78" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B78" s="1" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A47" s="2" t="s">
+    <row r="79" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A79" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B79" s="1" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A48" s="2" t="s">
+    <row r="80" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A80" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B80" s="1" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A49" s="2" t="s">
+    <row r="81" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A81" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B81" s="1" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A50" s="2" t="s">
+    <row r="82" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A82" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B82" s="1" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A51" s="2" t="s">
+    <row r="83" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A83" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B83" s="1" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A52" s="2" t="s">
+    <row r="84" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A84" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B84" s="1" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A53" s="2" t="s">
+    <row r="85" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A85" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B85" s="1" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A54" s="2" t="s">
+    <row r="86" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A86" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B86" s="1" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A55" s="2" t="s">
+    <row r="87" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A87" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B87" s="1" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A56" s="2" t="s">
+    <row r="88" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A88" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A89" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A90" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A91" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A92" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A93" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A94" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A95" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A96" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A97" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A98" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A99" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A100" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A101" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A102" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A103" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A104" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A105" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A106" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B106" s="1" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A57" s="2" t="s">
+    <row r="107" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A107" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B107" s="1" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A58" s="2" t="s">
+    <row r="108" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A108" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B108" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A59" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A60" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A61" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A62" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A63" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A64" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A65" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A66" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A67" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A68" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A69" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A70" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A71" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A72" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A73" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A74" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A75" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>560</v>
+    <row r="109" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A109" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A110" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A111" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A112" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A113" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A114" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A115" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A116" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A117" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A118" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A119" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A120" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A121" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A122" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A123" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>666</v>
       </c>
     </row>
   </sheetData>
@@ -2745,7 +3423,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B62"/>
+  <dimension ref="A1:B64"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -2760,152 +3438,152 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
         <v>372</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A5" t="s">
         <v>374</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A6" t="s">
         <v>376</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A7" t="s">
         <v>392</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A8" t="s">
         <v>393</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A9" t="s">
         <v>390</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A10" t="s">
         <v>391</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A11" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A12" t="s">
         <v>380</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A13" t="s">
         <v>384</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A14" t="s">
         <v>386</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A15" t="s">
         <v>382</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A16" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A17" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A18" s="2" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A18" t="s">
         <v>366</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A19" s="2" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A19" t="s">
         <v>368</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="1" t="s">
         <v>370</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -2913,7 +3591,7 @@
       </c>
     </row>
     <row r="21" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -2921,7 +3599,7 @@
       </c>
     </row>
     <row r="22" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -2929,7 +3607,7 @@
       </c>
     </row>
     <row r="23" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -2937,7 +3615,7 @@
       </c>
     </row>
     <row r="24" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -2945,7 +3623,7 @@
       </c>
     </row>
     <row r="25" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -2953,7 +3631,7 @@
       </c>
     </row>
     <row r="26" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="1" t="s">
         <v>482</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -2961,7 +3639,7 @@
       </c>
     </row>
     <row r="27" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -2969,7 +3647,7 @@
       </c>
     </row>
     <row r="28" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -2977,7 +3655,7 @@
       </c>
     </row>
     <row r="29" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -2985,7 +3663,7 @@
       </c>
     </row>
     <row r="30" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -2993,7 +3671,7 @@
       </c>
     </row>
     <row r="31" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="1" t="s">
         <v>378</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -3001,7 +3679,7 @@
       </c>
     </row>
     <row r="32" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -3009,7 +3687,7 @@
       </c>
     </row>
     <row r="33" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -3017,7 +3695,7 @@
       </c>
     </row>
     <row r="34" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -3025,39 +3703,39 @@
       </c>
     </row>
     <row r="35" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="1" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="1" t="s">
         <v>422</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -3065,186 +3743,202 @@
       </c>
     </row>
     <row r="40" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="1" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A42" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B42" s="1" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A42" s="2" t="s">
+    <row r="43" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A43" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B43" s="1" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A43" s="2" t="s">
+    <row r="44" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A44" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B44" s="1" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A44" s="4" t="s">
+    <row r="45" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A45" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B45" s="1" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A45" s="2" t="s">
+    <row r="46" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A46" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B46" s="1" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A46" s="2" t="s">
+    <row r="47" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A47" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B47" s="1" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A47" s="2" t="s">
+    <row r="48" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A48" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A49" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B49" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A48" s="2" t="s">
+    <row r="50" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A50" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B50" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A49" s="2" t="s">
+    <row r="51" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A51" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B51" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A50" s="2" t="s">
+    <row r="52" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A52" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B52" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A51" s="2" t="s">
+    <row r="53" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A53" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B53" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A52" s="2" t="s">
+    <row r="54" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A54" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B54" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A53" s="2" t="s">
+    <row r="55" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A55" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B55" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A54" s="2" t="s">
+    <row r="56" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A56" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B56" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A55" s="2" t="s">
+    <row r="57" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A57" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B57" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A56" s="2" t="s">
+    <row r="58" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B58" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A57" s="2" t="s">
+    <row r="59" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A59" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B59" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A58" s="2" t="s">
+    <row r="60" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A60" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B60" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A59" s="2" t="s">
+    <row r="61" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A61" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B61" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A60" s="4" t="s">
+    <row r="62" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A62" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B62" s="1" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A61" s="4" t="s">
+    <row r="63" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A63" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B63" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
-      <c r="A62" s="2" t="s">
+    <row r="64" spans="1:2" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A64" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B64" s="1" t="s">
         <v>70</v>
       </c>
     </row>
